--- a/AAII_Financials/Quarterly/RYAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RYAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>RYAN</t>
   </si>
@@ -656,269 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>902700</v>
+      </c>
+      <c r="E8" s="3">
         <v>782900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>738000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>739600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>840900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>676100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>649400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>588100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>680200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>537900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>518700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>487300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>573000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>447500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>435000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>412000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>878200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>386900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>378500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>352800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>390000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>311500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1018300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>236800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>246300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>208200</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>513400</v>
+      </c>
+      <c r="E9" s="3">
         <v>476100</v>
       </c>
-      <c r="E9" s="3">
-        <v>419300</v>
-      </c>
       <c r="F9" s="3">
-        <v>429400</v>
+        <v>436800</v>
       </c>
       <c r="G9" s="3">
-        <v>474500</v>
+        <v>424600</v>
       </c>
       <c r="H9" s="3">
+        <v>468300</v>
+      </c>
+      <c r="I9" s="3">
         <v>412000</v>
       </c>
-      <c r="I9" s="3">
-        <v>355800</v>
-      </c>
       <c r="J9" s="3">
+        <v>381600</v>
+      </c>
+      <c r="K9" s="3">
         <v>368000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>406200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>339500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>327700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>315600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>349900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>305400</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,53 +968,56 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>389400</v>
+      </c>
+      <c r="E10" s="3">
         <v>306800</v>
       </c>
-      <c r="E10" s="3">
-        <v>318700</v>
-      </c>
       <c r="F10" s="3">
-        <v>310200</v>
+        <v>301300</v>
       </c>
       <c r="G10" s="3">
-        <v>366400</v>
+        <v>314900</v>
       </c>
       <c r="H10" s="3">
+        <v>372600</v>
+      </c>
+      <c r="I10" s="3">
         <v>264100</v>
       </c>
-      <c r="I10" s="3">
-        <v>293600</v>
-      </c>
       <c r="J10" s="3">
+        <v>267800</v>
+      </c>
+      <c r="K10" s="3">
         <v>220100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>274000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>198400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>191000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>171800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>223100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>142100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,8 +1060,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,8 +1096,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1172,8 +1186,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,88 +1278,91 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E14" s="3">
         <v>53000</v>
       </c>
-      <c r="E14" s="3">
-        <v>70500</v>
-      </c>
       <c r="F14" s="3">
-        <v>38400</v>
+        <v>53100</v>
       </c>
       <c r="G14" s="3">
+        <v>43100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>30100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>36200</v>
+      </c>
+      <c r="K14" s="3">
+        <v>59200</v>
+      </c>
+      <c r="L14" s="3">
+        <v>28500</v>
+      </c>
+      <c r="M14" s="3">
+        <v>46700</v>
+      </c>
+      <c r="N14" s="3">
+        <v>17900</v>
+      </c>
+      <c r="O14" s="3">
+        <v>26200</v>
+      </c>
+      <c r="P14" s="3">
+        <v>24500</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>12900</v>
+      </c>
+      <c r="S14" s="3">
+        <v>20900</v>
+      </c>
+      <c r="T14" s="3">
+        <v>54300</v>
+      </c>
+      <c r="U14" s="3">
+        <v>28400</v>
+      </c>
+      <c r="V14" s="3">
         <v>23900</v>
       </c>
-      <c r="H14" s="3">
-        <v>17700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>44000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>59200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>28500</v>
-      </c>
-      <c r="L14" s="3">
-        <v>46700</v>
-      </c>
-      <c r="M14" s="3">
-        <v>17900</v>
-      </c>
-      <c r="N14" s="3">
-        <v>26200</v>
-      </c>
-      <c r="O14" s="3">
-        <v>24500</v>
-      </c>
-      <c r="P14" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="W14" s="3">
+        <v>61900</v>
+      </c>
+      <c r="X14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3">
         <v>12900</v>
       </c>
-      <c r="R14" s="3">
-        <v>20900</v>
-      </c>
-      <c r="S14" s="3">
-        <v>54300</v>
-      </c>
-      <c r="T14" s="3">
-        <v>28400</v>
-      </c>
-      <c r="U14" s="3">
-        <v>23900</v>
-      </c>
-      <c r="V14" s="3">
-        <v>61900</v>
-      </c>
-      <c r="W14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>12900</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4400</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1350,97 +1370,103 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E15" s="3">
         <v>69400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>73500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>73800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>72600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>67600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>63100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>30100</v>
       </c>
       <c r="M15" s="3">
         <v>30100</v>
       </c>
       <c r="N15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="O15" s="3">
         <v>31800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>26500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>26800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>27100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>55300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>27900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>27000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>28500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>29000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>67500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>16700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>10000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10800</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1495,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>676700</v>
+      </c>
+      <c r="E17" s="3">
         <v>646900</v>
       </c>
-      <c r="E17" s="3">
-        <v>597800</v>
-      </c>
       <c r="F17" s="3">
-        <v>605000</v>
+        <v>615300</v>
       </c>
       <c r="G17" s="3">
-        <v>640400</v>
+        <v>600300</v>
       </c>
       <c r="H17" s="3">
+        <v>634200</v>
+      </c>
+      <c r="I17" s="3">
         <v>571900</v>
       </c>
-      <c r="I17" s="3">
-        <v>497100</v>
-      </c>
       <c r="J17" s="3">
+        <v>523000</v>
+      </c>
+      <c r="K17" s="3">
         <v>480600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>502800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>434400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>421700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>405900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>437800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>379500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>355800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>350700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>729300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>343500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>323300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>353500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>297800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>271600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>859700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>211000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>188600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>181700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>226100</v>
+      </c>
+      <c r="E18" s="3">
         <v>136000</v>
       </c>
-      <c r="E18" s="3">
-        <v>140200</v>
-      </c>
       <c r="F18" s="3">
-        <v>134500</v>
+        <v>122800</v>
       </c>
       <c r="G18" s="3">
-        <v>200500</v>
+        <v>139300</v>
       </c>
       <c r="H18" s="3">
+        <v>206700</v>
+      </c>
+      <c r="I18" s="3">
         <v>104300</v>
       </c>
-      <c r="I18" s="3">
-        <v>152300</v>
-      </c>
       <c r="J18" s="3">
+        <v>126400</v>
+      </c>
+      <c r="K18" s="3">
         <v>107500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>177400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>103500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>97000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>81400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>135300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>68000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>79200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>61300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>148900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>55200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>92300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>39900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>158600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>25800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>57700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,444 +1713,457 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4900</v>
       </c>
-      <c r="I20" s="3">
-        <v>17300</v>
-      </c>
       <c r="J20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-16100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-21400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-31900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E21" s="3">
         <v>210900</v>
       </c>
-      <c r="E21" s="3">
-        <v>213700</v>
-      </c>
       <c r="F21" s="3">
-        <v>213300</v>
+        <v>196200</v>
       </c>
       <c r="G21" s="3">
-        <v>278200</v>
+        <v>218000</v>
       </c>
       <c r="H21" s="3">
+        <v>284400</v>
+      </c>
+      <c r="I21" s="3">
         <v>176800</v>
       </c>
-      <c r="I21" s="3">
-        <v>198100</v>
-      </c>
       <c r="J21" s="3">
+        <v>190400</v>
+      </c>
+      <c r="K21" s="3">
         <v>153300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>214000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>139200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>112700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>115400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>163300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>97500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>107800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>88700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>196800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>63200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>81500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>113300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>47500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>194200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>68200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>34400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E22" s="3">
         <v>53700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>45800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>56300</v>
       </c>
-      <c r="G22" s="3">
-        <v>58300</v>
-      </c>
       <c r="H22" s="3">
+        <v>57400</v>
+      </c>
+      <c r="I22" s="3">
         <v>54500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>57600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>49400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>31100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>28900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>29500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>29400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>46600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>47200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8700</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E23" s="3">
         <v>47100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>59800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>137700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>69000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>136700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>40500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>95500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>42800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>51600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>32700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>94900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>35400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-38000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>65700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>79500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>51500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E24" s="3">
         <v>6500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>55400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>1600</v>
       </c>
       <c r="AB24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
+      <c r="AC24" s="3">
+        <v>1600</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
@@ -2125,8 +2171,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,186 +2263,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E26" s="3">
         <v>40600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>62600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>124700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>42600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>118000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>40700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>58500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>83800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>45800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>88200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-32600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>63400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>70500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>49900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>13300</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E27" s="3">
         <v>17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>31100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>52000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>45200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>63400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>68100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>49900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12300</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2570,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,186 +2815,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4900</v>
       </c>
-      <c r="I32" s="3">
-        <v>-17300</v>
-      </c>
       <c r="J32" s="3">
+        <v>800</v>
+      </c>
+      <c r="K32" s="3">
         <v>4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>16100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>21400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>31900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E33" s="3">
         <v>17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>52000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>63400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>68100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>49900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12300</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3091,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E35" s="3">
         <v>17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>52000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>63400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>68100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>49900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12300</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,77 +3350,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E41" s="3">
         <v>154700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>158300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>153500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>172600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>203500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>540200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>235200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>612400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>665400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>838800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>754400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>966000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>704700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>992700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>833100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>866700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>706400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>387000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>413700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>307500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>159200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3440,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3365,20 +3455,20 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>3100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3442,77 +3532,80 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>720700</v>
+      </c>
+      <c r="E43" s="3">
         <v>594000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>526400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>480600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>555900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>458700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>434100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>373200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>424900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>336100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>330700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>276300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>340000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>266000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2871700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2339000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3066800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2316400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2602900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>172900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>208100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>159500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3624,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3575,8 +3671,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3620,77 +3716,80 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5709600</v>
+      </c>
+      <c r="E45" s="3">
         <v>4764300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4298900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3747100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4474800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3888700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3739700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3357000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4051000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3181400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3131700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2521000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3327700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2475200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1944300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2325400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1830800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,77 +3808,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6642600</v>
+      </c>
+      <c r="E46" s="3">
         <v>5578800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5060200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4446800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5266300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4609100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4788900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4019400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5122500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4216400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4335600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3586400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4659400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3468900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3894100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3199600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3955400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3040600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3011000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2530900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2841100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2149400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,77 +3900,80 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>121700</v>
+      </c>
+      <c r="E47" s="3">
         <v>116400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>110000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>101800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>96000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>72400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>70900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>75600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>88200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>89400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>75800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>92100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>90800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>78400</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>38500</v>
       </c>
       <c r="R47" s="3">
         <v>38500</v>
       </c>
       <c r="S47" s="3">
+        <v>38500</v>
+      </c>
+      <c r="T47" s="3">
         <v>40500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>41800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>45400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>47100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>46900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>46600</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3887,77 +3992,80 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E48" s="3">
         <v>191900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>199900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>204300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>200700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>192000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>183500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>168300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>167700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>164300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>170100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>164000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>169000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>173500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>175100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>158000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>148000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>114300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>100200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>95300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>102500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>106100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3976,77 +4084,80 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4716200</v>
+      </c>
+      <c r="E49" s="3">
         <v>4777900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4841500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4749700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4720900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4677000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4122400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3694000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2487600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2239000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2257200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2173600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1873000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1893800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1801400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1815600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1838200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1863400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1883200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1751800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1777200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1802500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4065,8 +4176,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,77 +4360,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E52" s="3">
         <v>34000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>24700</v>
       </c>
       <c r="K52" s="3">
         <v>24700</v>
       </c>
       <c r="L52" s="3">
+        <v>24700</v>
+      </c>
+      <c r="M52" s="3">
         <v>21300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>474600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>476300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>460200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>425500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>418900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>433400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>39500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>45700</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4452,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,77 +4544,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11966600</v>
+      </c>
+      <c r="E54" s="3">
         <v>11011600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10564200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9851900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10625800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9890000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9649900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8478500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8272400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7116500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7247200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6425900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7235800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6047000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6383700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5688000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6442400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5485600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5458700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4858500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4807100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4150300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4636,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,77 +4706,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E57" s="3">
         <v>237700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>217300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>202800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>166000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>179600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>191000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>137900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>174800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>127400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>96200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>91000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>119000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>79500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>101300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>99400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>78800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>131900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>122300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,77 +4796,80 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E58" s="3">
         <v>62600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>86200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>85100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>58500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>73800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>54800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>55500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>49700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>42900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>30600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>29200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>28900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>23500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>22500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21900</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4754,77 +4888,80 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5898300</v>
+      </c>
+      <c r="E59" s="3">
         <v>4898400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4366000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3827100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4529500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3930700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3797900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3425300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4108400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3237300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3140600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2539800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3332600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2486200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2984800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2406700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3238900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2381300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2795300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2271300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2706000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2025700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,77 +4980,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6655600</v>
+      </c>
+      <c r="E60" s="3">
         <v>5456000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5188700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4456900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5233500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4398600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4549100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3965900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4696100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3677400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3744300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2981800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3827500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2766600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3134400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2517800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3347300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2505300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2918100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2376900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2860500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2169900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,77 +5072,80 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3717200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3680100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3444600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3508600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3567800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3808500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3390400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2795000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2090300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2090200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2098300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2102500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2110700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2101700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1951900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1953500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1955000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1956600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1566600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1568400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1570200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1572000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5021,77 +5164,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>532100</v>
+      </c>
+      <c r="E62" s="3">
         <v>609200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>627000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>616700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>601100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>586700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>572300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>594900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>412800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>374100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>424900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>400200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>353500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>326400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>479700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>459100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>438500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>399700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>379200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>358100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>156200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>167600</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5256,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,77 +5532,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10950500</v>
+      </c>
+      <c r="E66" s="3">
         <v>9792600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9310100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8620000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9443600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8832700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8551600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7377000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7199200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6141700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6267600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5484600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6291900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5195400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5905300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5245200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6033200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5113700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5114900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4545700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4586900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3909500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5624,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5740,14 +5908,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>240800</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>314500</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5766,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,77 +6026,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>145300</v>
+      </c>
+      <c r="E72" s="3">
         <v>120500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>120400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>128800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>115400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>79300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>122900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>125000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>121600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>88500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>114400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>92200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>97200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>67100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>54000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-369600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-418900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6118,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,77 +6394,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>509400</v>
+      </c>
+      <c r="E76" s="3">
         <v>636200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>648100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>630500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>610100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>542500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>627700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>632800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>605900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>554400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>559800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>543000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>558900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>508600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>478400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>442700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>409300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>371900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>343800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>312700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-20600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-73700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6486,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6578,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E81" s="3">
         <v>17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>52000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>63400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>68100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>49900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12300</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,97 +6803,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E83" s="3">
         <v>8500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>7900</v>
       </c>
       <c r="G83" s="3">
         <v>7900</v>
       </c>
       <c r="H83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I83" s="3">
         <v>7800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1200</v>
       </c>
       <c r="P83" s="3">
         <v>1200</v>
       </c>
       <c r="Q83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R83" s="3">
         <v>26800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>27100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>55300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>28200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>28500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>29000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>67500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10800</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,97 +7353,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-167400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>263200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>169700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>353600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-142800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>259600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>270800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-116500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>226900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>105500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>304000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-159200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>184500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>164700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-65500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>119100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>46700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>182500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-74800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>135400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-66100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>100400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-32000</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,97 +7481,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-345600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,97 +7755,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-88200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-45900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-573000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-469300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1049700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-229100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-94300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-272700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-104900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-112500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-345300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-768500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-813200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,41 +7883,42 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E96" s="3">
         <v>16800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>15500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>16300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>15400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>15100</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
         <v>13500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>13000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>40000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
@@ -7694,8 +7928,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7739,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,271 +8249,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E100" s="3">
         <v>86300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>72800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-229100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-102500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>336800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>541500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>553200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>82400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>19300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-182800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>180400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>54400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-119400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>379800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>308700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>83200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>365500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>56700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-76100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1125300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>983700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-73700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>103600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E101" s="3">
         <v>10100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-99600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>210600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-144900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>206900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-368900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>324700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-388000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>122800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-135000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>153300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-350100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>479300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-293600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>229400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-139700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>538000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>241400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>90400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>66000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>241100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-153500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>493500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>105500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>24200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>31100</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
